--- a/src/assets/updateBill.xlsx
+++ b/src/assets/updateBill.xlsx
@@ -1,26 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milan\codes\unicode\SVKM_Bill_Tracking_Frontend\src\assets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054B27F2-BD5C-4F97-AB98-1B7E60D76713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Bills Report" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Bills Report" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Notes" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="38">
   <si>
     <t>Sr no</t>
   </si>
@@ -40,6 +32,9 @@
     <t>MIGO Amt</t>
   </si>
   <si>
+    <t>MIGO done by</t>
+  </si>
+  <si>
     <t>SES no</t>
   </si>
   <si>
@@ -49,6 +44,15 @@
     <t>SES Dt</t>
   </si>
   <si>
+    <t>SES done by</t>
+  </si>
+  <si>
+    <t>Dt ret-PIMO aft approval</t>
+  </si>
+  <si>
+    <t>Payment Instructions</t>
+  </si>
+  <si>
     <t>F110</t>
   </si>
   <si>
@@ -73,119 +77,269 @@
     <t>MIRO Amt</t>
   </si>
   <si>
-    <t>MIGO done by</t>
-  </si>
-  <si>
-    <t>SES done by</t>
-  </si>
-  <si>
-    <t>Dt ret-PIMO aft approval</t>
+    <t>Column Heading</t>
+  </si>
+  <si>
+    <t>Use By</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>Mandatory</t>
+  </si>
+  <si>
+    <t>7 digit no on the Home tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QS team </t>
+  </si>
+  <si>
+    <t>Date should be in dd-mm-yyyy format only</t>
+  </si>
+  <si>
+    <t>Amt should be in Number format without comma</t>
+  </si>
+  <si>
+    <t>Site team</t>
+  </si>
+  <si>
+    <t>10 digit no only as per SAP</t>
+  </si>
+  <si>
+    <t>Name of MIGO done by</t>
+  </si>
+  <si>
+    <t>PIMO Mumbai Team</t>
+  </si>
+  <si>
+    <t>Name of SES done by</t>
+  </si>
+  <si>
+    <t>Accounts Team</t>
+  </si>
+  <si>
+    <t>Alpha Numeric text</t>
+  </si>
+  <si>
+    <t>SV000/HD000</t>
+  </si>
+  <si>
+    <t>Specify either Yes or No only</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="5">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="12.0"/>
+      <color/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
     <font>
-      <sz val="8"/>
+      <sz val="11.0"/>
+      <color/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <color/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92CDDC"/>
+        <bgColor rgb="FF92CDDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="14">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBE5F1"/>
+          <bgColor rgb="FFDBE5F1"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+      <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="1">
+    <tableStyle count="3" pivot="0" name="Bills Report-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19E0A45D-E3AE-7C4D-9DD6-EFA7371ABCD4}" name="Table2" displayName="Table2" ref="A1:T2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:T2" xr:uid="{19E0A45D-E3AE-7C4D-9DD6-EFA7371ABCD4}"/>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{C20F23A7-8BB1-AF4B-954E-6399C6DC33F6}" name="Sr no"/>
-    <tableColumn id="41" xr3:uid="{C598F594-ADB8-194D-BC84-D3870539FFF9}" name="COP Dt"/>
-    <tableColumn id="42" xr3:uid="{4DC8FA1F-A5CB-5247-B6CF-7E8092E22723}" name="COP Amt" dataDxfId="1"/>
-    <tableColumn id="46" xr3:uid="{0883B355-C2FB-B043-9367-F80EEB2452A2}" name="MIGO no"/>
-    <tableColumn id="47" xr3:uid="{25B13C71-C2A5-EF4B-8E6F-160C97D5DEB7}" name="MIGO Dt"/>
-    <tableColumn id="48" xr3:uid="{C8B94CE0-E57C-8845-8599-1D0DB90F906B}" name="MIGO Amt"/>
-    <tableColumn id="2" xr3:uid="{67894A11-211D-4DCA-B1C0-14285A21BC28}" name="MIGO done by"/>
-    <tableColumn id="72" xr3:uid="{FACDFCE5-E71F-7E46-83D8-CFFA08031FEF}" name="SES no"/>
-    <tableColumn id="73" xr3:uid="{2B7C0437-3388-1941-AF4D-F23C4F240AFB}" name="SES Amt"/>
-    <tableColumn id="74" xr3:uid="{6CA554FF-9BEA-4D42-937F-577A2F209FF4}" name="SES Dt"/>
-    <tableColumn id="3" xr3:uid="{B3DB1DA1-B6D0-484D-A028-7701F5FC47EB}" name="SES done by"/>
-    <tableColumn id="4" xr3:uid="{5B8A3B07-7364-46D8-8BC9-34FC6298728B}" name="Dt ret-PIMO aft approval"/>
-    <tableColumn id="90" xr3:uid="{FA6833F9-DF1E-B344-9B2B-8BCA6D49AF6B}" name="F110"/>
-    <tableColumn id="91" xr3:uid="{CB3D8C37-4C1B-D845-81F9-668AB18EF7CE}" name="Dt of Payment"/>
-    <tableColumn id="92" xr3:uid="{D1A422AA-B7AD-C34B-ADC0-9EEA8012389C}" name="Hard Copy"/>
-    <tableColumn id="93" xr3:uid="{E4074CA4-7AE8-4441-9AD8-4C224D043561}" name="Accts Identification"/>
-    <tableColumn id="94" xr3:uid="{93EBCE8E-0CA1-2C4E-BF86-0F1F8D307200}" name="Payment Amt" dataDxfId="0"/>
-    <tableColumn id="97" xr3:uid="{12E7C22A-90D3-3D48-B586-C2A20019C122}" name="MIRO no"/>
-    <tableColumn id="98" xr3:uid="{13B8112B-3DE5-934D-AB4D-CA1783E53E0B}" name="MIRO Dt"/>
-    <tableColumn id="99" xr3:uid="{C5F567A5-8543-2E45-9A94-29405ED168BA}" name="MIRO Amt"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:U2" displayName="Table_1" name="Table_1" id="1">
+  <tableColumns count="21">
+    <tableColumn name="Sr no" id="1"/>
+    <tableColumn name="COP Dt" id="2"/>
+    <tableColumn name="COP Amt" id="3"/>
+    <tableColumn name="MIGO no" id="4"/>
+    <tableColumn name="MIGO Dt" id="5"/>
+    <tableColumn name="MIGO Amt" id="6"/>
+    <tableColumn name="MIGO done by" id="7"/>
+    <tableColumn name="SES no" id="8"/>
+    <tableColumn name="SES Amt" id="9"/>
+    <tableColumn name="SES Dt" id="10"/>
+    <tableColumn name="SES done by" id="11"/>
+    <tableColumn name="Dt ret-PIMO aft approval" id="12"/>
+    <tableColumn name="Payment Instructions" id="13"/>
+    <tableColumn name="F110" id="14"/>
+    <tableColumn name="Dt of Payment" id="15"/>
+    <tableColumn name="Hard Copy" id="16"/>
+    <tableColumn name="Accts Identification" id="17"/>
+    <tableColumn name="Payment Amt" id="18"/>
+    <tableColumn name="MIRO no" id="19"/>
+    <tableColumn name="MIRO Dt" id="20"/>
+    <tableColumn name="MIRO Amt" id="21"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="Bills Report-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -339,7 +493,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="9525" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -348,13 +502,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="25400" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="38100" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -364,7 +518,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="20000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -373,7 +527,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -382,7 +536,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" rotWithShape="0" dir="5400000" dist="23000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -392,12 +546,12 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
+            <a:lightRig dir="t" rig="threePt">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
+            <a:bevelT h="25400" w="63500"/>
           </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
@@ -428,7 +582,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+            <a:fillToRect b="180000" l="50000" r="50000" t="-80000"/>
           </a:path>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
@@ -447,7 +601,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+            <a:fillToRect b="50000" l="50000" r="50000" t="50000"/>
           </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -498,93 +652,1672 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="10" width="15.84765625" customWidth="1"/>
-    <col min="11" max="11" width="20.34765625" customWidth="1"/>
-    <col min="12" max="12" width="15.84765625" customWidth="1"/>
-    <col min="13" max="13" width="30.84765625" customWidth="1"/>
-    <col min="14" max="14" width="17.34765625" customWidth="1"/>
-    <col min="15" max="17" width="15.84765625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="15.88"/>
+    <col customWidth="1" min="2" max="2" width="45.25"/>
+    <col customWidth="1" min="3" max="10" width="15.88"/>
+    <col customWidth="1" min="11" max="11" width="20.38"/>
+    <col customWidth="1" min="12" max="12" width="15.88"/>
+    <col customWidth="1" min="13" max="13" width="30.88"/>
+    <col customWidth="1" min="14" max="14" width="17.38"/>
+    <col customWidth="1" min="15" max="17" width="15.88"/>
+    <col customWidth="1" min="18" max="21" width="10.75"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.6">
-      <c r="A1" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.6">
-      <c r="C2" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.6">
-      <c r="C3" s="1"/>
-      <c r="N3" s="1"/>
-    </row>
+      <c r="R2" s="4"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1"/>
+    <row r="4" ht="15.75" customHeight="1"/>
+    <row r="5" ht="15.75" customHeight="1"/>
+    <row r="6" ht="15.75" customHeight="1"/>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="26.0"/>
+    <col customWidth="1" min="2" max="2" width="35.88"/>
+    <col customWidth="1" min="3" max="3" width="31.75"/>
+    <col customWidth="1" min="4" max="4" width="34.25"/>
+    <col customWidth="1" min="5" max="5" width="35.88"/>
+    <col customWidth="1" min="6" max="6" width="34.25"/>
+    <col customWidth="1" min="7" max="11" width="10.75"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="5"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="5"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="5"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="5"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="5"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="5"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="5"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="5"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>